--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 13,07,26 млрсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 13,07,26 млрсч ост зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF401F74-D5EA-45F8-B509-8032201A99B3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B55653-78DF-4450-98FB-33DBBC4BC68D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -151,6 +148,12 @@
   </si>
   <si>
     <t>матрица</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>20,07,</t>
   </si>
 </sst>
 </file>
@@ -746,25 +749,25 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -809,19 +812,21 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>23</v>
+      <c r="Q4" s="1" t="s">
+        <v>41</v>
       </c>
-      <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -895,7 +900,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -910,7 +915,7 @@
       <c r="V5" s="1"/>
       <c r="W5" s="4">
         <f>SUM(W6:W500)</f>
-        <v>197.4</v>
+        <v>195.5</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -941,10 +946,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1">
         <v>120</v>
@@ -963,7 +968,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -996,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="V6" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W6" s="1">
-        <f>G6*Q6</f>
+        <f t="shared" ref="W6:W16" si="2">G6*Q6</f>
         <v>0</v>
       </c>
       <c r="X6" s="1"/>
@@ -1031,10 +1036,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
@@ -1049,7 +1054,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1061,16 +1066,16 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1">
-        <f t="shared" ref="P7:P16" si="2">E7/5</f>
+        <f t="shared" ref="P7:P16" si="3">E7/5</f>
         <v>0</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="1" t="e">
-        <f t="shared" ref="R7:R16" si="3">(F7+Q7)/P7</f>
+        <f t="shared" ref="R7:R16" si="4">(F7+Q7)/P7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S7" s="1" t="e">
-        <f t="shared" ref="S7:S16" si="4">F7/P7</f>
+        <f t="shared" ref="S7:S16" si="5">F7/P7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T7" s="1">
@@ -1081,7 +1086,7 @@
       </c>
       <c r="V7" s="1"/>
       <c r="W7" s="1">
-        <f>G7*Q7</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X7" s="1"/>
@@ -1113,10 +1118,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
@@ -1131,7 +1136,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1143,16 +1148,16 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="1" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S8" s="1" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T8" s="1">
@@ -1163,7 +1168,7 @@
       </c>
       <c r="V8" s="1"/>
       <c r="W8" s="1">
-        <f>G8*Q8</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X8" s="1"/>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1">
         <v>120</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1225,16 +1230,16 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="1" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S9" s="1" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T9" s="1">
@@ -1244,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W9" s="1">
-        <f>G9*Q9</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X9" s="1"/>
@@ -1279,10 +1284,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
@@ -1299,7 +1304,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1313,19 +1318,18 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>19.600000000000001</v>
       </c>
       <c r="Q10" s="5">
-        <f t="shared" ref="Q7:Q16" si="5">15*P10-F10</f>
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" si="3"/>
-        <v>14.999999999999998</v>
+        <f t="shared" si="4"/>
+        <v>14.795918367346937</v>
       </c>
       <c r="S10" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.6938775510204067</v>
       </c>
       <c r="T10" s="1">
@@ -1336,8 +1340,8 @@
       </c>
       <c r="V10" s="1"/>
       <c r="W10" s="1">
-        <f>G10*Q10</f>
-        <v>31.2</v>
+        <f t="shared" si="2"/>
+        <v>30</v>
       </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
@@ -1368,10 +1372,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1">
@@ -1388,7 +1392,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1402,16 +1406,16 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.2</v>
       </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>55</v>
       </c>
       <c r="S11" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>55</v>
       </c>
       <c r="T11" s="1">
@@ -1422,7 +1426,7 @@
       </c>
       <c r="V11" s="1"/>
       <c r="W11" s="1">
-        <f>G11*Q11</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X11" s="1"/>
@@ -1454,10 +1458,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
@@ -1474,7 +1478,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1488,19 +1492,18 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20.2</v>
       </c>
       <c r="Q12" s="5">
-        <f t="shared" si="5"/>
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="R12" s="1">
-        <f t="shared" si="3"/>
-        <v>15</v>
+        <f t="shared" si="4"/>
+        <v>15.099009900990099</v>
       </c>
       <c r="S12" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.24752475247524752</v>
       </c>
       <c r="T12" s="1">
@@ -1511,8 +1514,8 @@
       </c>
       <c r="V12" s="1"/>
       <c r="W12" s="1">
-        <f>G12*Q12</f>
-        <v>107.8</v>
+        <f t="shared" si="2"/>
+        <v>108.5</v>
       </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
@@ -1543,10 +1546,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
@@ -1563,7 +1566,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1577,16 +1580,16 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="S13" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="T13" s="1">
@@ -1597,7 +1600,7 @@
       </c>
       <c r="V13" s="1"/>
       <c r="W13" s="1">
-        <f>G13*Q13</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X13" s="1"/>
@@ -1629,10 +1632,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
@@ -1649,7 +1652,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1663,19 +1666,18 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20.6</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" si="5"/>
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="R14" s="1">
-        <f t="shared" si="3"/>
-        <v>14.999999999999998</v>
+        <f t="shared" si="4"/>
+        <v>14.805825242718445</v>
       </c>
       <c r="S14" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.9805825242718438</v>
       </c>
       <c r="T14" s="1">
@@ -1686,8 +1688,8 @@
       </c>
       <c r="V14" s="1"/>
       <c r="W14" s="1">
-        <f>G14*Q14</f>
-        <v>43.4</v>
+        <f t="shared" si="2"/>
+        <v>42</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
@@ -1718,10 +1720,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -1732,7 +1734,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1744,18 +1746,18 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q15" s="5">
         <v>50</v>
       </c>
       <c r="R15" s="1" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S15" s="1" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T15" s="1">
@@ -1766,7 +1768,7 @@
       </c>
       <c r="V15" s="1"/>
       <c r="W15" s="1">
-        <f>G15*Q15</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="X15" s="1"/>
@@ -1798,10 +1800,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
@@ -1818,7 +1820,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -1832,16 +1834,16 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10.6</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>32.735849056603776</v>
       </c>
       <c r="S16" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>32.735849056603776</v>
       </c>
       <c r="T16" s="1">
@@ -1852,7 +1854,7 @@
       </c>
       <c r="V16" s="1"/>
       <c r="W16" s="1">
-        <f>G16*Q16</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X16" s="1"/>
